--- a/Configs/GameConfig/Datas/fg/#LootPick-三选一候选池.xlsx
+++ b/Configs/GameConfig/Datas/fg/#LootPick-三选一候选池.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3917,6 +3917,366 @@
         <v>162</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>pick.foundry.fw.fw_bouncefuse</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>fw_bouncefuse</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>pick.clarity.fw.fw_coolback</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>fw_coolback</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>pick.foundry.fw.fw_enterfuse</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>fw_enterfuse</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>pick.foundry.fw.fw_piercefuse</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>fw_piercefuse</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>pick.foundry.fw.fw_scuttle</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>fw_scuttle</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>pick.silent.fw.fw_uplinkpulse</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>fw_uplinkpulse</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>pick.silent.fw.fw_ventarc</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>fw_ventarc</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>pick.clarity.fw.fw_water</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>firmware</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>encrypted_firmware</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>fw_water</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1007</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
